--- a/diseases/d162/2026-2029.xlsx
+++ b/diseases/d162/2026-2029.xlsx
@@ -13458,13 +13458,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O66" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R66" t="n">
-        <v>0.2134571005036965</v>
+        <v>0.2312451922123379</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -13622,10 +13622,10 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O67" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
@@ -14657,13 +14657,13 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>0.03557618341728275</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -14821,10 +14821,10 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U73" t="inlineStr">
         <is>
@@ -15574,7 +15574,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1409</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d162/2026-2029.xlsx
+++ b/diseases/d162/2026-2029.xlsx
@@ -13861,13 +13861,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="O68" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="R68" t="n">
-        <v>0.1592078243215956</v>
+        <v>0.283036132127281</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -14025,10 +14025,10 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="O69" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="U69" t="inlineStr">
         <is>
@@ -15060,13 +15060,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O74" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>0.05306927477386519</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -15224,10 +15224,10 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O75" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U75" t="inlineStr">
         <is>
@@ -15574,7 +15574,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1412</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d162/2026-2029.xlsx
+++ b/diseases/d162/2026-2029.xlsx
@@ -4724,10 +4724,10 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O22" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -4880,10 +4880,10 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O23" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
@@ -8688,10 +8688,10 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="O42" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -8844,10 +8844,10 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="O43" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
@@ -10670,10 +10670,10 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="O52" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -10826,10 +10826,10 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="O53" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="U53" t="inlineStr">
         <is>
@@ -12220,12 +12220,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -12259,22 +12259,19 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="O60" t="n">
-        <v>7</v>
-      </c>
-      <c r="R60" t="n">
-        <v>0.1245166419604896</v>
+        <v>48</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_CA_ON_PHO_IDTO_HIV_MONTHLY</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -12289,70 +12286,65 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ60" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR60" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_CA_ON_PHO_IDTO_HIV_MONTHLY</t>
         </is>
       </c>
       <c r="AT60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC60" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -12384,12 +12376,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -12423,29 +12415,29 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="O61" t="n">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_CA_ON_PHO_IDTO_HIV_MONTHLY</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_CA_ON_PHO_IDTO_HIV_MONTHLY</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CA_ON_PHO_IDTO</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>HIV, total</t>
+          <t>HIV</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
@@ -12455,7 +12447,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -12470,7 +12462,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CA-ON:national</t>
         </is>
       </c>
       <c r="AD61" t="inlineStr">
@@ -12505,17 +12497,17 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>PHO_IDTO_2026_07</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Use the THL all-stage total; HIV not AIDS is an overlapping child and is not projected.</t>
+          <t>PHO IDTO current-year monthly HIV counts include eligible carrier/carrier and case/confirmed encounters and are classified by Encounter Date (Reported Date). The series includes patients who progressed to AIDS and is not mutually exclusive with the AIDS series.</t>
         </is>
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -12528,70 +12520,65 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ61" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR61" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_CA_ON_PHO_IDTO_HIV_MONTHLY</t>
         </is>
       </c>
       <c r="AT61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC61" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -12623,12 +12610,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -12662,13 +12649,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="O62" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="R62" t="n">
-        <v>0.2299668573534158</v>
+        <v>0.1245166419604896</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -12677,7 +12664,7 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -12697,7 +12684,7 @@
       </c>
       <c r="AQ62" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR62" t="inlineStr">
@@ -12707,7 +12694,7 @@
       </c>
       <c r="AS62" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AT62" t="n">
@@ -12715,47 +12702,47 @@
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC62" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -12787,12 +12774,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -12826,29 +12813,29 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="O63" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>Hiv-infeksjon</t>
+          <t>HIV, total</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
@@ -12873,7 +12860,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD63" t="inlineStr">
@@ -12908,17 +12895,17 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS HIV infection kept distinct from AIDS.</t>
+          <t>Finland THL national monthly notification series; Use the THL all-stage total; HIV not AIDS is an overlapping child and is not projected.</t>
         </is>
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -12936,7 +12923,7 @@
       </c>
       <c r="AQ63" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR63" t="inlineStr">
@@ -12946,7 +12933,7 @@
       </c>
       <c r="AS63" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AT63" t="n">
@@ -12954,47 +12941,47 @@
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC63" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -13026,12 +13013,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -13065,13 +13052,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>89</v>
+        <v>13</v>
       </c>
       <c r="O64" t="n">
-        <v>89</v>
+        <v>13</v>
       </c>
       <c r="R64" t="n">
-        <v>0.3867666277328837</v>
+        <v>0.2299668573534158</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -13080,7 +13067,7 @@
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -13095,7 +13082,7 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ64" t="inlineStr">
@@ -13103,57 +13090,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS64" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AT64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC64" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -13185,12 +13177,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -13224,29 +13216,29 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>89</v>
+        <v>13</v>
       </c>
       <c r="O65" t="n">
-        <v>89</v>
+        <v>13</v>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>SRC_TW_NIDSS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>人類免疫缺乏病毒感染(含母子垂直感染及孕產婦疑似個案)</t>
+          <t>Hiv-infeksjon</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr">
@@ -13256,7 +13248,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -13271,7 +13263,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>country:TW:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD65" t="inlineStr">
@@ -13286,7 +13278,7 @@
       </c>
       <c r="AF65" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG65" t="inlineStr">
@@ -13306,17 +13298,17 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>NIDSS disease code 044, including source-specified vertical transmission and suspected maternal cases.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS HIV infection kept distinct from AIDS.</t>
         </is>
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -13329,7 +13321,7 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ65" t="inlineStr">
@@ -13337,57 +13329,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS65" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AT65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB65" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC65" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -13419,12 +13416,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -13449,22 +13446,22 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N66" t="n">
-        <v>13</v>
+        <v>89</v>
       </c>
       <c r="O66" t="n">
-        <v>13</v>
+        <v>89</v>
       </c>
       <c r="R66" t="n">
-        <v>0.2312451922123379</v>
+        <v>0.3867666277328837</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -13473,7 +13470,7 @@
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -13488,70 +13485,65 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ66" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR66" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="AT66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB66" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC66" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -13583,12 +13575,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -13613,38 +13605,38 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N67" t="n">
-        <v>13</v>
+        <v>89</v>
       </c>
       <c r="O67" t="n">
-        <v>13</v>
+        <v>89</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_TW_NIDSS</t>
         </is>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>HIV, total</t>
+          <t>人類免疫缺乏病毒感染(含母子垂直感染及孕產婦疑似個案)</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr">
@@ -13654,7 +13646,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -13669,7 +13661,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:TW:national</t>
         </is>
       </c>
       <c r="AD67" t="inlineStr">
@@ -13684,7 +13676,7 @@
       </c>
       <c r="AF67" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG67" t="inlineStr">
@@ -13704,12 +13696,12 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Use the THL all-stage total; HIV not AIDS is an overlapping child and is not projected.</t>
+          <t>NIDSS disease code 044, including source-specified vertical transmission and suspected maternal cases.</t>
         </is>
       </c>
       <c r="AM67" t="inlineStr">
@@ -13727,70 +13719,65 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ67" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR67" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="AT67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB67" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC67" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -13822,12 +13809,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -13861,13 +13848,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="O68" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="R68" t="n">
-        <v>0.283036132127281</v>
+        <v>0.2312451922123379</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -13876,7 +13863,7 @@
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -13896,7 +13883,7 @@
       </c>
       <c r="AQ68" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR68" t="inlineStr">
@@ -13906,7 +13893,7 @@
       </c>
       <c r="AS68" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AT68" t="n">
@@ -13914,47 +13901,47 @@
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB68" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC68" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -13986,12 +13973,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -14025,29 +14012,29 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="O69" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>Hiv-infeksjon</t>
+          <t>HIV, total</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr">
@@ -14072,7 +14059,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD69" t="inlineStr">
@@ -14107,17 +14094,17 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS HIV infection kept distinct from AIDS.</t>
+          <t>Finland THL national monthly notification series; Use the THL all-stage total; HIV not AIDS is an overlapping child and is not projected.</t>
         </is>
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14135,7 +14122,7 @@
       </c>
       <c r="AQ69" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR69" t="inlineStr">
@@ -14145,7 +14132,7 @@
       </c>
       <c r="AS69" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AT69" t="n">
@@ -14153,47 +14140,47 @@
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB69" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC69" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -14225,12 +14212,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -14264,13 +14251,13 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="O70" t="n">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="R70" t="n">
-        <v>0.1607906205181651</v>
+        <v>0.283036132127281</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -14279,7 +14266,7 @@
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -14294,7 +14281,7 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ70" t="inlineStr">
@@ -14302,57 +14289,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS70" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AT70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB70" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC70" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -14384,12 +14376,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -14423,29 +14415,29 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="O71" t="n">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>SRC_TW_NIDSS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>人類免疫缺乏病毒感染(含母子垂直感染及孕產婦疑似個案)</t>
+          <t>Hiv-infeksjon</t>
         </is>
       </c>
       <c r="Y71" t="inlineStr">
@@ -14455,7 +14447,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -14470,7 +14462,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>country:TW:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD71" t="inlineStr">
@@ -14485,7 +14477,7 @@
       </c>
       <c r="AF71" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG71" t="inlineStr">
@@ -14505,17 +14497,17 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>NIDSS disease code 044, including source-specified vertical transmission and suspected maternal cases.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS HIV infection kept distinct from AIDS.</t>
         </is>
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -14528,7 +14520,7 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ71" t="inlineStr">
@@ -14536,57 +14528,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR71" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS71" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AT71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC71" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -14618,12 +14615,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -14648,22 +14645,22 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N72" t="n">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="O72" t="n">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="R72" t="n">
-        <v>0.03557618341728275</v>
+        <v>0.1607906205181651</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -14672,7 +14669,7 @@
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -14687,70 +14684,65 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ72" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR72" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="AT72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB72" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC72" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -14782,12 +14774,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -14812,38 +14804,38 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N73" t="n">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="O73" t="n">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="W73" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_TW_NIDSS</t>
         </is>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>HIV, total</t>
+          <t>人類免疫缺乏病毒感染(含母子垂直感染及孕產婦疑似個案)</t>
         </is>
       </c>
       <c r="Y73" t="inlineStr">
@@ -14853,7 +14845,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -14868,7 +14860,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:TW:national</t>
         </is>
       </c>
       <c r="AD73" t="inlineStr">
@@ -14883,7 +14875,7 @@
       </c>
       <c r="AF73" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG73" t="inlineStr">
@@ -14903,12 +14895,12 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Use the THL all-stage total; HIV not AIDS is an overlapping child and is not projected.</t>
+          <t>NIDSS disease code 044, including source-specified vertical transmission and suspected maternal cases.</t>
         </is>
       </c>
       <c r="AM73" t="inlineStr">
@@ -14926,70 +14918,65 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ73" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR73" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="AT73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC73" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -15021,12 +15008,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -15060,13 +15047,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O74" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R74" t="n">
-        <v>0.05306927477386519</v>
+        <v>0.03557618341728275</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -15075,7 +15062,7 @@
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -15095,7 +15082,7 @@
       </c>
       <c r="AQ74" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR74" t="inlineStr">
@@ -15105,7 +15092,7 @@
       </c>
       <c r="AS74" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AT74" t="n">
@@ -15113,47 +15100,47 @@
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC74" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -15185,12 +15172,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -15224,29 +15211,29 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="W75" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>Hiv-infeksjon</t>
+          <t>HIV, total</t>
         </is>
       </c>
       <c r="Y75" t="inlineStr">
@@ -15271,7 +15258,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD75" t="inlineStr">
@@ -15306,17 +15293,17 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS HIV infection kept distinct from AIDS.</t>
+          <t>Finland THL national monthly notification series; Use the THL all-stage total; HIV not AIDS is an overlapping child and is not projected.</t>
         </is>
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -15334,7 +15321,7 @@
       </c>
       <c r="AQ75" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR75" t="inlineStr">
@@ -15344,7 +15331,7 @@
       </c>
       <c r="AS75" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AT75" t="n">
@@ -15352,45 +15339,448 @@
       </c>
       <c r="AU75" t="inlineStr">
         <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV75" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA75" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB75" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC75" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>hiv-infection</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>人类免疫缺乏病毒感染</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O76" t="n">
+        <v>3</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0.05306927477386519</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP76" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ76" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT76" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
-      <c r="AV75" t="inlineStr">
+      <c r="AV76" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW75" t="inlineStr">
+      <c r="AW76" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
+      <c r="AX76" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY75" t="inlineStr">
+      <c r="AY76" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
+      <c r="AZ76" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA75" t="inlineStr">
+      <c r="BA76" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB75" t="inlineStr">
+      <c r="BB76" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC75" t="inlineStr">
+      <c r="BC76" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>hiv-infection</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>人类免疫缺乏病毒感染</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>3</v>
+      </c>
+      <c r="O77" t="n">
+        <v>3</v>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>Hiv-infeksjon</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD77" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE77" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF77" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG77" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS HIV infection kept distinct from AIDS.</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN77" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP77" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ77" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT77" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV77" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA77" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB77" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC77" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -15512,7 +15902,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10">
@@ -15522,7 +15912,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11">
@@ -15542,7 +15932,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13">
@@ -15574,7 +15964,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1422</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d162/2026-2029.xlsx
+++ b/diseases/d162/2026-2029.xlsx
@@ -15047,13 +15047,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O74" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R74" t="n">
-        <v>0.03557618341728275</v>
+        <v>0.07115236683456549</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -15211,10 +15211,10 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O75" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U75" t="inlineStr">
         <is>
@@ -15964,7 +15964,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1463</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d162/2026-2029.xlsx
+++ b/diseases/d162/2026-2029.xlsx
@@ -15047,13 +15047,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O74" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R74" t="n">
-        <v>0.07115236683456549</v>
+        <v>0.08894045854320688</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -15211,10 +15211,10 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O75" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U75" t="inlineStr">
         <is>
@@ -15964,7 +15964,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1465</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d162/2026-2029.xlsx
+++ b/diseases/d162/2026-2029.xlsx
@@ -15450,13 +15450,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O76" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R76" t="n">
-        <v>0.05306927477386519</v>
+        <v>0.08844879128977531</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -15614,10 +15614,10 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O77" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
@@ -15964,7 +15964,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1466</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d162/2026-2029.xlsx
+++ b/diseases/d162/2026-2029.xlsx
@@ -1391,7 +1391,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3373,7 +3373,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5355,7 +5355,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7337,7 +7337,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9319,7 +9319,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10518,7 +10518,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -12107,7 +12107,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -13696,7 +13696,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14895,7 +14895,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15047,13 +15047,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="O74" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="R74" t="n">
-        <v>0.08894045854320688</v>
+        <v>0.2490332839209793</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -15211,10 +15211,10 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="O75" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="U75" t="inlineStr">
         <is>
@@ -15450,13 +15450,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O76" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R76" t="n">
-        <v>0.08844879128977531</v>
+        <v>0.1238283078056854</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -15614,10 +15614,10 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O77" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
@@ -15964,7 +15964,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1468</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d162/2026-2029.xlsx
+++ b/diseases/d162/2026-2029.xlsx
@@ -15047,13 +15047,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="O74" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="R74" t="n">
-        <v>0.2490332839209793</v>
+        <v>0.3201856507555447</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -15211,10 +15211,10 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="O75" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="U75" t="inlineStr">
         <is>
@@ -15783,6 +15783,409 @@
       <c r="BC77" t="inlineStr">
         <is>
           <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>hiv-infection</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>人类免疫缺乏病毒感染</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_150</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP78" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ78" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_150</t>
+        </is>
+      </c>
+      <c r="AT78" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV78" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA78" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB78" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC78" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>hiv-infection</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>人类免疫缺乏病毒感染</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_150</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_150</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>HIV, total</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD79" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE79" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF79" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG79" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use the THL all-stage total; HIV not AIDS is an overlapping child and is not projected.</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN79" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP79" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ79" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_150</t>
+        </is>
+      </c>
+      <c r="AT79" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV79" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA79" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB79" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC79" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -15819,7 +16222,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -15902,7 +16305,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10">
@@ -15912,7 +16315,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11">
@@ -15932,7 +16335,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13">
@@ -15964,7 +16367,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1479</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d162/2026-2029.xlsx
+++ b/diseases/d162/2026-2029.xlsx
@@ -2202,7 +2202,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -8148,7 +8148,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -10130,7 +10130,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -11719,7 +11719,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -13308,7 +13308,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -14507,7 +14507,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -15450,13 +15450,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="O76" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="R76" t="n">
-        <v>0.1238283078056854</v>
+        <v>0.2299668573534158</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -15614,10 +15614,10 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="O77" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
@@ -15706,7 +15706,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -16367,7 +16367,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1483</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d162/2026-2029.xlsx
+++ b/diseases/d162/2026-2029.xlsx
@@ -2202,7 +2202,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -6706,10 +6706,10 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O32" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -6862,10 +6862,10 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O33" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
@@ -8148,7 +8148,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8688,10 +8688,10 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="O42" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -8844,10 +8844,10 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="O43" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10670,10 +10670,10 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="O52" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -10826,10 +10826,10 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="O53" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="U53" t="inlineStr">
         <is>
@@ -11021,12 +11021,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -11060,13 +11060,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="O54" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="R54" t="n">
-        <v>0.2490332839209793</v>
+        <v>0.3663492453982649</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -11075,7 +11075,7 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_CH_HIV_MONTHLY</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -11090,70 +11090,65 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ54" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR54" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_CH_HIV_MONTHLY</t>
         </is>
       </c>
       <c r="AT54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="BC54" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
     </row>
@@ -11185,12 +11180,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -11224,29 +11219,29 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="O55" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_CH_HIV_MONTHLY</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_CH_HIV_MONTHLY</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CH_FOPH_IDD</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>HIV, total</t>
+          <t>Human Immunodeficiency Virus (HIV)</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
@@ -11256,7 +11251,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -11271,7 +11266,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CH:national</t>
         </is>
       </c>
       <c r="AD55" t="inlineStr">
@@ -11286,7 +11281,7 @@
       </c>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG55" t="inlineStr">
@@ -11306,17 +11301,17 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Use the THL all-stage total; HIV not AIDS is an overlapping child and is not projected.</t>
+          <t>Source-reported HIV diagnoses at any reported stage.</t>
         </is>
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -11329,70 +11324,65 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ55" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR55" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_CH_HIV_MONTHLY</t>
         </is>
       </c>
       <c r="AT55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="BC55" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
     </row>
@@ -11424,12 +11414,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -11463,13 +11453,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O56" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="R56" t="n">
-        <v>0.283036132127281</v>
+        <v>0.2490332839209793</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -11478,7 +11468,7 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -11498,7 +11488,7 @@
       </c>
       <c r="AQ56" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR56" t="inlineStr">
@@ -11508,7 +11498,7 @@
       </c>
       <c r="AS56" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AT56" t="n">
@@ -11516,47 +11506,47 @@
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC56" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -11588,12 +11578,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -11627,29 +11617,29 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O57" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Hiv-infeksjon</t>
+          <t>HIV, total</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
@@ -11674,7 +11664,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD57" t="inlineStr">
@@ -11709,17 +11699,17 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS HIV infection kept distinct from AIDS.</t>
+          <t>Finland THL national monthly notification series; Use the THL all-stage total; HIV not AIDS is an overlapping child and is not projected.</t>
         </is>
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -11737,7 +11727,7 @@
       </c>
       <c r="AQ57" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR57" t="inlineStr">
@@ -11747,7 +11737,7 @@
       </c>
       <c r="AS57" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AT57" t="n">
@@ -11755,47 +11745,47 @@
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC57" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -11827,12 +11817,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -11866,13 +11856,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="O58" t="n">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="R58" t="n">
-        <v>0.4345692446436896</v>
+        <v>0.283036132127281</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -11881,7 +11871,7 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -11896,7 +11886,7 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ58" t="inlineStr">
@@ -11904,57 +11894,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS58" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AT58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC58" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -11986,12 +11981,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -12025,29 +12020,29 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="O59" t="n">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>SRC_TW_NIDSS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>人類免疫缺乏病毒感染(含母子垂直感染及孕產婦疑似個案)</t>
+          <t>Hiv-infeksjon</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
@@ -12057,7 +12052,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -12072,7 +12067,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>country:TW:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr">
@@ -12087,7 +12082,7 @@
       </c>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG59" t="inlineStr">
@@ -12107,17 +12102,17 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>NIDSS disease code 044, including source-specified vertical transmission and suspected maternal cases.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS HIV infection kept distinct from AIDS.</t>
         </is>
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12130,7 +12125,7 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ59" t="inlineStr">
@@ -12138,57 +12133,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR59" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS59" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AT59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC59" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -12220,12 +12220,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CA-ON</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ontario, Canada</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -12250,28 +12250,31 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N60" t="n">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="O60" t="n">
-        <v>48</v>
+        <v>100</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0.4345692446436896</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>SER_CA_ON_PHO_IDTO_HIV_MONTHLY</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -12296,7 +12299,7 @@
       </c>
       <c r="AS60" t="inlineStr">
         <is>
-          <t>SER_CA_ON_PHO_IDTO_HIV_MONTHLY</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="AT60" t="n">
@@ -12309,42 +12312,42 @@
       </c>
       <c r="AV60" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC60" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -12376,12 +12379,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CA-ON</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Ontario, Canada</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -12406,38 +12409,38 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N61" t="n">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="O61" t="n">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>SER_CA_ON_PHO_IDTO_HIV_MONTHLY</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>SER_CA_ON_PHO_IDTO_HIV_MONTHLY</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>SRC_CA_ON_PHO_IDTO</t>
+          <t>SRC_TW_NIDSS</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>HIV</t>
+          <t>人類免疫缺乏病毒感染(含母子垂直感染及孕產婦疑似個案)</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
@@ -12462,7 +12465,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>country:CA-ON:national</t>
+          <t>country:TW:national</t>
         </is>
       </c>
       <c r="AD61" t="inlineStr">
@@ -12477,7 +12480,7 @@
       </c>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG61" t="inlineStr">
@@ -12497,17 +12500,17 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>PHO_IDTO_2026_07</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>PHO IDTO current-year monthly HIV counts include eligible carrier/carrier and case/confirmed encounters and are classified by Encounter Date (Reported Date). The series includes patients who progressed to AIDS and is not mutually exclusive with the AIDS series.</t>
+          <t>NIDSS disease code 044, including source-specified vertical transmission and suspected maternal cases.</t>
         </is>
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -12530,7 +12533,7 @@
       </c>
       <c r="AS61" t="inlineStr">
         <is>
-          <t>SER_CA_ON_PHO_IDTO_HIV_MONTHLY</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="AT61" t="n">
@@ -12543,42 +12546,42 @@
       </c>
       <c r="AV61" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC61" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -12610,12 +12613,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -12649,22 +12652,19 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="O62" t="n">
-        <v>7</v>
-      </c>
-      <c r="R62" t="n">
-        <v>0.1245166419604896</v>
+        <v>47</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_CA_ON_PHO_IDTO_HIV_MONTHLY</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -12679,70 +12679,65 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ62" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR62" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_CA_ON_PHO_IDTO_HIV_MONTHLY</t>
         </is>
       </c>
       <c r="AT62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC62" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -12774,12 +12769,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -12813,29 +12808,29 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="O63" t="n">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_CA_ON_PHO_IDTO_HIV_MONTHLY</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_CA_ON_PHO_IDTO_HIV_MONTHLY</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CA_ON_PHO_IDTO</t>
         </is>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>HIV, total</t>
+          <t>HIV</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
@@ -12845,7 +12840,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -12860,7 +12855,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CA-ON:national</t>
         </is>
       </c>
       <c r="AD63" t="inlineStr">
@@ -12895,17 +12890,17 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>PHO_IDTO_2026_07</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Use the THL all-stage total; HIV not AIDS is an overlapping child and is not projected.</t>
+          <t>PHO IDTO current-year monthly HIV counts include eligible carrier/carrier and case/confirmed encounters and are classified by Encounter Date (Reported Date). The series includes patients who progressed to AIDS and is not mutually exclusive with the AIDS series.</t>
         </is>
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -12918,70 +12913,65 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ63" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR63" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_CA_ON_PHO_IDTO_HIV_MONTHLY</t>
         </is>
       </c>
       <c r="AT63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC63" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -13013,12 +13003,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -13052,13 +13042,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="O64" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="R64" t="n">
-        <v>0.2299668573534158</v>
+        <v>0.1245166419604896</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -13067,7 +13057,7 @@
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -13087,7 +13077,7 @@
       </c>
       <c r="AQ64" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR64" t="inlineStr">
@@ -13097,7 +13087,7 @@
       </c>
       <c r="AS64" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AT64" t="n">
@@ -13105,47 +13095,47 @@
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC64" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -13177,12 +13167,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -13216,29 +13206,29 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="O65" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>Hiv-infeksjon</t>
+          <t>HIV, total</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr">
@@ -13263,7 +13253,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD65" t="inlineStr">
@@ -13298,17 +13288,17 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS HIV infection kept distinct from AIDS.</t>
+          <t>Finland THL national monthly notification series; Use the THL all-stage total; HIV not AIDS is an overlapping child and is not projected.</t>
         </is>
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -13326,7 +13316,7 @@
       </c>
       <c r="AQ65" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR65" t="inlineStr">
@@ -13336,7 +13326,7 @@
       </c>
       <c r="AS65" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AT65" t="n">
@@ -13344,47 +13334,47 @@
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB65" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC65" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -13416,12 +13406,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -13455,13 +13445,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>89</v>
+        <v>13</v>
       </c>
       <c r="O66" t="n">
-        <v>89</v>
+        <v>13</v>
       </c>
       <c r="R66" t="n">
-        <v>0.3867666277328837</v>
+        <v>0.2299668573534158</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -13470,7 +13460,7 @@
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -13485,7 +13475,7 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ66" t="inlineStr">
@@ -13493,57 +13483,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS66" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AT66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB66" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC66" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -13575,12 +13570,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -13614,29 +13609,29 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>89</v>
+        <v>13</v>
       </c>
       <c r="O67" t="n">
-        <v>89</v>
+        <v>13</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>SRC_TW_NIDSS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>人類免疫缺乏病毒感染(含母子垂直感染及孕產婦疑似個案)</t>
+          <t>Hiv-infeksjon</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr">
@@ -13646,7 +13641,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -13661,7 +13656,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>country:TW:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD67" t="inlineStr">
@@ -13676,7 +13671,7 @@
       </c>
       <c r="AF67" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG67" t="inlineStr">
@@ -13696,17 +13691,17 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>NIDSS disease code 044, including source-specified vertical transmission and suspected maternal cases.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS HIV infection kept distinct from AIDS.</t>
         </is>
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -13719,7 +13714,7 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ67" t="inlineStr">
@@ -13727,57 +13722,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS67" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AT67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB67" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC67" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -13809,12 +13809,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -13839,22 +13839,22 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N68" t="n">
-        <v>13</v>
+        <v>89</v>
       </c>
       <c r="O68" t="n">
-        <v>13</v>
+        <v>89</v>
       </c>
       <c r="R68" t="n">
-        <v>0.2312451922123379</v>
+        <v>0.3867666277328837</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -13863,7 +13863,7 @@
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -13878,70 +13878,65 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ68" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR68" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="AT68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB68" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC68" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -13973,12 +13968,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -14003,38 +13998,38 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N69" t="n">
-        <v>13</v>
+        <v>89</v>
       </c>
       <c r="O69" t="n">
-        <v>13</v>
+        <v>89</v>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_TW_NIDSS</t>
         </is>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>HIV, total</t>
+          <t>人類免疫缺乏病毒感染(含母子垂直感染及孕產婦疑似個案)</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr">
@@ -14044,7 +14039,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -14059,7 +14054,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:TW:national</t>
         </is>
       </c>
       <c r="AD69" t="inlineStr">
@@ -14074,7 +14069,7 @@
       </c>
       <c r="AF69" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG69" t="inlineStr">
@@ -14094,12 +14089,12 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Use the THL all-stage total; HIV not AIDS is an overlapping child and is not projected.</t>
+          <t>NIDSS disease code 044, including source-specified vertical transmission and suspected maternal cases.</t>
         </is>
       </c>
       <c r="AM69" t="inlineStr">
@@ -14117,70 +14112,65 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ69" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR69" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="AT69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB69" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC69" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -14212,12 +14202,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -14251,22 +14241,19 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="O70" t="n">
-        <v>16</v>
-      </c>
-      <c r="R70" t="n">
-        <v>0.283036132127281</v>
+        <v>56</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_CA_ON_PHO_IDTO_HIV_MONTHLY</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -14281,7 +14268,7 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ70" t="inlineStr">
@@ -14289,62 +14276,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR70" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS70" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_CA_ON_PHO_IDTO_HIV_MONTHLY</t>
         </is>
       </c>
       <c r="AT70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB70" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC70" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -14376,12 +14358,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -14415,29 +14397,29 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="O71" t="n">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_CA_ON_PHO_IDTO_HIV_MONTHLY</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_CA_ON_PHO_IDTO_HIV_MONTHLY</t>
         </is>
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CA_ON_PHO_IDTO</t>
         </is>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>Hiv-infeksjon</t>
+          <t>HIV</t>
         </is>
       </c>
       <c r="Y71" t="inlineStr">
@@ -14447,7 +14429,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -14462,7 +14444,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CA-ON:national</t>
         </is>
       </c>
       <c r="AD71" t="inlineStr">
@@ -14497,17 +14479,17 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>PHO_IDTO_2026_07</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS HIV infection kept distinct from AIDS.</t>
+          <t>PHO IDTO current-year monthly HIV counts include eligible carrier/carrier and case/confirmed encounters and are classified by Encounter Date (Reported Date). The series includes patients who progressed to AIDS and is not mutually exclusive with the AIDS series.</t>
         </is>
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -14520,7 +14502,7 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ71" t="inlineStr">
@@ -14528,62 +14510,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR71" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS71" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_CA_ON_PHO_IDTO_HIV_MONTHLY</t>
         </is>
       </c>
       <c r="AT71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC71" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -14615,12 +14592,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -14654,13 +14631,13 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="O72" t="n">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="R72" t="n">
-        <v>0.1607906205181651</v>
+        <v>0.2312451922123379</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -14669,7 +14646,7 @@
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -14684,65 +14661,70 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ72" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR72" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AT72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB72" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC72" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -14774,12 +14756,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -14813,29 +14795,29 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="O73" t="n">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="W73" t="inlineStr">
         <is>
-          <t>SRC_TW_NIDSS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>人類免疫缺乏病毒感染(含母子垂直感染及孕產婦疑似個案)</t>
+          <t>HIV, total</t>
         </is>
       </c>
       <c r="Y73" t="inlineStr">
@@ -14845,7 +14827,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -14860,7 +14842,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>country:TW:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD73" t="inlineStr">
@@ -14875,7 +14857,7 @@
       </c>
       <c r="AF73" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG73" t="inlineStr">
@@ -14895,12 +14877,12 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>NIDSS disease code 044, including source-specified vertical transmission and suspected maternal cases.</t>
+          <t>Finland THL national monthly notification series; Use the THL all-stage total; HIV not AIDS is an overlapping child and is not projected.</t>
         </is>
       </c>
       <c r="AM73" t="inlineStr">
@@ -14918,65 +14900,70 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ73" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR73" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AT73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC73" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -15008,12 +14995,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -15038,22 +15025,22 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N74" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O74" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R74" t="n">
-        <v>0.3201856507555447</v>
+        <v>0.283036132127281</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -15062,7 +15049,7 @@
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -15082,7 +15069,7 @@
       </c>
       <c r="AQ74" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR74" t="inlineStr">
@@ -15092,7 +15079,7 @@
       </c>
       <c r="AS74" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AT74" t="n">
@@ -15100,47 +15087,47 @@
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC74" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -15172,12 +15159,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -15202,38 +15189,38 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N75" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O75" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="W75" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>HIV, total</t>
+          <t>Hiv-infeksjon</t>
         </is>
       </c>
       <c r="Y75" t="inlineStr">
@@ -15258,7 +15245,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD75" t="inlineStr">
@@ -15293,17 +15280,17 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Use the THL all-stage total; HIV not AIDS is an overlapping child and is not projected.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS HIV infection kept distinct from AIDS.</t>
         </is>
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -15321,7 +15308,7 @@
       </c>
       <c r="AQ75" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR75" t="inlineStr">
@@ -15331,7 +15318,7 @@
       </c>
       <c r="AS75" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AT75" t="n">
@@ -15339,47 +15326,47 @@
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC75" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -15411,12 +15398,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -15441,22 +15428,22 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N76" t="n">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="O76" t="n">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="R76" t="n">
-        <v>0.2299668573534158</v>
+        <v>0.1607906205181651</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -15465,7 +15452,7 @@
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -15480,7 +15467,7 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ76" t="inlineStr">
@@ -15488,62 +15475,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR76" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS76" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="AT76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC76" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -15575,12 +15557,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -15605,38 +15587,38 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N77" t="n">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="O77" t="n">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="W77" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_TW_NIDSS</t>
         </is>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>Hiv-infeksjon</t>
+          <t>人類免疫缺乏病毒感染(含母子垂直感染及孕產婦疑似個案)</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
@@ -15646,7 +15628,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -15661,7 +15643,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:TW:national</t>
         </is>
       </c>
       <c r="AD77" t="inlineStr">
@@ -15676,7 +15658,7 @@
       </c>
       <c r="AF77" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG77" t="inlineStr">
@@ -15696,17 +15678,17 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS HIV infection kept distinct from AIDS.</t>
+          <t>NIDSS disease code 044, including source-specified vertical transmission and suspected maternal cases.</t>
         </is>
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -15719,7 +15701,7 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ77" t="inlineStr">
@@ -15727,62 +15709,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR77" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS77" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="AT77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC77" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -15844,22 +15821,22 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O78" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>0.3201856507555447</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -16008,19 +15985,19 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O79" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="U79" t="inlineStr">
         <is>
@@ -16186,6 +16163,1215 @@
       <c r="BC79" t="inlineStr">
         <is>
           <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>hiv-infection</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>人类免疫缺乏病毒感染</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>15</v>
+      </c>
+      <c r="O80" t="n">
+        <v>15</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0.2653463738693259</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP80" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ80" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT80" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV80" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA80" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB80" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC80" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>hiv-infection</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>人类免疫缺乏病毒感染</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>15</v>
+      </c>
+      <c r="O81" t="n">
+        <v>15</v>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>Hiv-infeksjon</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD81" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE81" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF81" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG81" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS HIV infection kept distinct from AIDS.</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN81" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP81" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ81" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT81" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV81" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA81" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB81" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC81" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>hiv-infection</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>人类免疫缺乏病毒感染</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" t="n">
+        <v>0</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_150</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP82" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ82" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR82" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS82" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_150</t>
+        </is>
+      </c>
+      <c r="AT82" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV82" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA82" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB82" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC82" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>hiv-infection</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>人类免疫缺乏病毒感染</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_150</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_150</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>HIV, total</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD83" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE83" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF83" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG83" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use the THL all-stage total; HIV not AIDS is an overlapping child and is not projected.</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN83" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP83" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ83" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_150</t>
+        </is>
+      </c>
+      <c r="AT83" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV83" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA83" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB83" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC83" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>hiv-infection</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>人类免疫缺乏病毒感染</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N84" t="n">
+        <v>1</v>
+      </c>
+      <c r="O84" t="n">
+        <v>1</v>
+      </c>
+      <c r="R84" t="n">
+        <v>0.01768975825795506</v>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP84" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ84" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR84" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS84" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT84" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV84" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA84" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB84" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC84" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>hiv-infection</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>人类免疫缺乏病毒感染</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>1</v>
+      </c>
+      <c r="O85" t="n">
+        <v>1</v>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>Hiv-infeksjon</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD85" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE85" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF85" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG85" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS HIV infection kept distinct from AIDS.</t>
+        </is>
+      </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN85" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP85" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ85" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR85" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS85" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT85" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV85" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA85" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB85" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC85" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -16305,7 +17491,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10">
@@ -16315,7 +17501,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11">
@@ -16335,7 +17521,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13">
@@ -16367,7 +17553,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1489</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d162/2026-2029.xlsx
+++ b/diseases/d162/2026-2029.xlsx
@@ -16636,13 +16636,13 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>0.03557618341728275</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -16800,10 +16800,10 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U83" t="inlineStr">
         <is>
@@ -17553,7 +17553,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1576</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d162/2026-2029.xlsx
+++ b/diseases/d162/2026-2029.xlsx
@@ -16233,13 +16233,13 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="O80" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="R80" t="n">
-        <v>0.2653463738693259</v>
+        <v>0.3184156486431911</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -16397,10 +16397,10 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="O81" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="U81" t="inlineStr">
         <is>
@@ -17039,13 +17039,13 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O84" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R84" t="n">
-        <v>0.01768975825795506</v>
+        <v>0.05306927477386519</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -17203,10 +17203,10 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O85" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U85" t="inlineStr">
         <is>
@@ -17553,7 +17553,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1578</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d162/2026-2029.xlsx
+++ b/diseases/d162/2026-2029.xlsx
@@ -6252,12 +6252,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN-GX</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Guangxi, China</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -6291,22 +6291,19 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>13</v>
+        <v>330</v>
       </c>
       <c r="O31" t="n">
-        <v>13</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0.2312451922123379</v>
+        <v>330</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_CN_PROV_REPORT_HIV_INFECTION</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -6321,70 +6318,65 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_CN_PROV_REPORT_HIV_INFECTION</t>
         </is>
       </c>
       <c r="AT31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/fdcrbyqgb/yqyb/</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -6416,12 +6408,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN-GX</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Guangxi, China</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -6455,29 +6447,29 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>13</v>
+        <v>330</v>
       </c>
       <c r="O32" t="n">
-        <v>13</v>
+        <v>330</v>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_CN_PROV_REPORT_HIV_INFECTION</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_CN_PROV_REPORT_HIV_INFECTION</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>HIV, total</t>
+          <t>HIV</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -6487,7 +6479,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -6502,7 +6494,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CN-GX:national</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
@@ -6537,17 +6529,17 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Use the THL all-stage total; HIV not AIDS is an overlapping child and is not projected.</t>
+          <t>Province-reported all-stage HIV infection count. Kept separate from AIDS (D005), which is a distinct disease stage and source category.</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN32" t="b">
@@ -6560,70 +6552,65 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_CN_PROV_REPORT_HIV_INFECTION</t>
         </is>
       </c>
       <c r="AT32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/fdcrbyqgb/yqyb/</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -6655,12 +6642,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -6694,13 +6681,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="O33" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="R33" t="n">
-        <v>0.3891746816750113</v>
+        <v>0.2312451922123379</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -6709,7 +6696,7 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -6729,7 +6716,7 @@
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR33" t="inlineStr">
@@ -6739,7 +6726,7 @@
       </c>
       <c r="AS33" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AT33" t="n">
@@ -6747,47 +6734,47 @@
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -6819,12 +6806,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -6858,29 +6845,29 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="O34" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Hiv-infeksjon</t>
+          <t>HIV, total</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -6905,7 +6892,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
@@ -6940,17 +6927,17 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS HIV infection kept distinct from AIDS.</t>
+          <t>Finland THL national monthly notification series; Use the THL all-stage total; HIV not AIDS is an overlapping child and is not projected.</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN34" t="b">
@@ -6968,7 +6955,7 @@
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR34" t="inlineStr">
@@ -6978,7 +6965,7 @@
       </c>
       <c r="AS34" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AT34" t="n">
@@ -6986,47 +6973,47 @@
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -7058,12 +7045,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -7097,13 +7084,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>93</v>
+        <v>22</v>
       </c>
       <c r="O35" t="n">
-        <v>93</v>
+        <v>22</v>
       </c>
       <c r="R35" t="n">
-        <v>0.4041493975186313</v>
+        <v>0.3891746816750113</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -7112,7 +7099,7 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -7127,7 +7114,7 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ35" t="inlineStr">
@@ -7135,57 +7122,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS35" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AT35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7209,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -7256,29 +7248,29 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>93</v>
+        <v>22</v>
       </c>
       <c r="O36" t="n">
-        <v>93</v>
+        <v>22</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>SRC_TW_NIDSS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>人類免疫缺乏病毒感染(含母子垂直感染及孕產婦疑似個案)</t>
+          <t>Hiv-infeksjon</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -7288,7 +7280,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -7303,7 +7295,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>country:TW:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr">
@@ -7318,7 +7310,7 @@
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG36" t="inlineStr">
@@ -7338,17 +7330,17 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.10.16.1</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>NIDSS disease code 044, including source-specified vertical transmission and suspected maternal cases.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS HIV infection kept distinct from AIDS.</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN36" t="b">
@@ -7361,7 +7353,7 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ36" t="inlineStr">
@@ -7369,57 +7361,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS36" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AT36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -7451,12 +7448,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>CA-ON</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ontario, Canada</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -7481,23 +7478,31 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N37" t="n">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="O37" t="n">
-        <v>62</v>
+        <v>93</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.4041493975186313</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -7507,66 +7512,70 @@
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS37" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ37" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS37" t="inlineStr">
+        <is>
+          <t>SER_TW_HIV_044</t>
+        </is>
+      </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC37" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -7593,17 +7602,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -7628,31 +7637,48 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N38" t="n">
-        <v>14</v>
+        <v>93</v>
       </c>
       <c r="O38" t="n">
-        <v>14</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0.2490332839209793</v>
-      </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>93</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_TW_HIV_044</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>SER_TW_HIV_044</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>SRC_TW_NIDSS</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>人類免疫缺乏病毒感染(含母子垂直感染及孕產婦疑似個案)</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -7660,6 +7686,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>country:TW:national</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>NIDSS disease code 044, including source-specified vertical transmission and suspected maternal cases.</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN38" t="b">
+        <v>1</v>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -7667,70 +7751,65 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ38" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="AT38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB38" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC38" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -7757,17 +7836,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -7801,39 +7880,14 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>14</v>
+        <v>62</v>
       </c>
       <c r="O39" t="n">
-        <v>14</v>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_150</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_150</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>HIV, total</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+        <v>62</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -7841,135 +7895,68 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD39" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG39" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use the THL all-stage total; HIV not AIDS is an overlapping child and is not projected.</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN39" t="b">
-        <v>1</v>
-      </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ39" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR39" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS39" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_150</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC39" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -8001,12 +7988,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CN-GX</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Guangxi, China</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -8040,22 +8027,19 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>16</v>
+        <v>380</v>
       </c>
       <c r="O40" t="n">
-        <v>16</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0.283036132127281</v>
+        <v>380</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_CN_PROV_REPORT_HIV_INFECTION</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -8070,7 +8054,7 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ40" t="inlineStr">
@@ -8078,62 +8062,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS40" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_CN_PROV_REPORT_HIV_INFECTION</t>
         </is>
       </c>
       <c r="AT40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB40" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/fdcrbyqgb/yqyb/</t>
         </is>
       </c>
       <c r="BC40" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -8165,12 +8144,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CN-GX</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Guangxi, China</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -8204,29 +8183,29 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>16</v>
+        <v>380</v>
       </c>
       <c r="O41" t="n">
-        <v>16</v>
+        <v>380</v>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_CN_PROV_REPORT_HIV_INFECTION</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_CN_PROV_REPORT_HIV_INFECTION</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Hiv-infeksjon</t>
+          <t>HIV</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
@@ -8236,7 +8215,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -8251,7 +8230,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CN-GX:national</t>
         </is>
       </c>
       <c r="AD41" t="inlineStr">
@@ -8286,17 +8265,17 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS HIV infection kept distinct from AIDS.</t>
+          <t>Province-reported all-stage HIV infection count. Kept separate from AIDS (D005), which is a distinct disease stage and source category.</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -8309,7 +8288,7 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ41" t="inlineStr">
@@ -8317,62 +8296,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS41" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_CN_PROV_REPORT_HIV_INFECTION</t>
         </is>
       </c>
       <c r="AT41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB41" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/fdcrbyqgb/yqyb/</t>
         </is>
       </c>
       <c r="BC41" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -8404,12 +8378,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -8443,13 +8417,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>100</v>
+        <v>14</v>
       </c>
       <c r="O42" t="n">
-        <v>100</v>
+        <v>14</v>
       </c>
       <c r="R42" t="n">
-        <v>0.4345692446436896</v>
+        <v>0.2490332839209793</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -8458,7 +8432,7 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -8473,65 +8447,70 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ42" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AT42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC42" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -8563,12 +8542,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -8602,29 +8581,29 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>100</v>
+        <v>14</v>
       </c>
       <c r="O43" t="n">
-        <v>100</v>
+        <v>14</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>SRC_TW_NIDSS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>人類免疫缺乏病毒感染(含母子垂直感染及孕產婦疑似個案)</t>
+          <t>HIV, total</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
@@ -8634,7 +8613,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -8649,7 +8628,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>country:TW:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD43" t="inlineStr">
@@ -8664,7 +8643,7 @@
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG43" t="inlineStr">
@@ -8684,12 +8663,12 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.10.16.1</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>NIDSS disease code 044, including source-specified vertical transmission and suspected maternal cases.</t>
+          <t>Finland THL national monthly notification series; Use the THL all-stage total; HIV not AIDS is an overlapping child and is not projected.</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
@@ -8707,65 +8686,70 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ43" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AT43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB43" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC43" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -8797,12 +8781,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>CA-ON</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ontario, Canada</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -8827,23 +8811,31 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N44" t="n">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="O44" t="n">
-        <v>47</v>
+        <v>16</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0.283036132127281</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -8853,66 +8845,75 @@
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ44" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR44" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS44" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS44" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC44" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -8939,17 +8940,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -8974,31 +8975,48 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N45" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="O45" t="n">
-        <v>7</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0.1245166419604896</v>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>16</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Hiv-infeksjon</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -9006,6 +9024,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS HIV infection kept distinct from AIDS.</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN45" t="b">
+        <v>1</v>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -9018,7 +9094,7 @@
       </c>
       <c r="AQ45" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR45" t="inlineStr">
@@ -9028,7 +9104,7 @@
       </c>
       <c r="AS45" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AT45" t="n">
@@ -9036,47 +9112,47 @@
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC45" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -9103,17 +9179,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -9138,48 +9214,31 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N46" t="n">
-        <v>7</v>
+        <v>100</v>
       </c>
       <c r="O46" t="n">
-        <v>7</v>
+        <v>100</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0.4345692446436896</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_150</t>
-        </is>
-      </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>HIV, total</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -9187,135 +9246,72 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD46" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE46" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF46" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG46" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use the THL all-stage total; HIV not AIDS is an overlapping child and is not projected.</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN46" t="b">
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP46" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ46" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS46" t="inlineStr">
+        <is>
+          <t>SER_TW_HIV_044</t>
+        </is>
+      </c>
+      <c r="AT46" t="n">
         <v>1</v>
       </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP46" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ46" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS46" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_150</t>
-        </is>
-      </c>
-      <c r="AT46" t="n">
-        <v>2</v>
-      </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC46" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -9342,17 +9338,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -9377,31 +9373,48 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N47" t="n">
-        <v>13</v>
+        <v>100</v>
       </c>
       <c r="O47" t="n">
-        <v>13</v>
-      </c>
-      <c r="R47" t="n">
-        <v>0.2299668573534158</v>
-      </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>100</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_TW_HIV_044</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>SER_TW_HIV_044</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>SRC_TW_NIDSS</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>人類免疫缺乏病毒感染(含母子垂直感染及孕產婦疑似個案)</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -9409,6 +9422,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>country:TW:national</t>
+        </is>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>NIDSS disease code 044, including source-specified vertical transmission and suspected maternal cases.</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN47" t="b">
+        <v>1</v>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -9416,7 +9487,7 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ47" t="inlineStr">
@@ -9424,62 +9495,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR47" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS47" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="AT47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB47" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC47" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -9506,17 +9572,17 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -9550,39 +9616,14 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="O48" t="n">
-        <v>13</v>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>Hiv-infeksjon</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+        <v>47</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -9590,135 +9631,68 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD48" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE48" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF48" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG48" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS HIV infection kept distinct from AIDS.</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN48" t="b">
-        <v>1</v>
-      </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ48" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR48" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS48" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB48" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC48" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -9750,12 +9724,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>CN-GX</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Guangxi, China</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -9789,22 +9763,19 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>89</v>
+        <v>364</v>
       </c>
       <c r="O49" t="n">
-        <v>89</v>
-      </c>
-      <c r="R49" t="n">
-        <v>0.3867666277328837</v>
+        <v>364</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_CN_PROV_REPORT_HIV_INFECTION</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -9829,7 +9800,7 @@
       </c>
       <c r="AS49" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_CN_PROV_REPORT_HIV_INFECTION</t>
         </is>
       </c>
       <c r="AT49" t="n">
@@ -9842,42 +9813,42 @@
       </c>
       <c r="AV49" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/fdcrbyqgb/yqyb/</t>
         </is>
       </c>
       <c r="BC49" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -9909,12 +9880,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>CN-GX</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Guangxi, China</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -9948,29 +9919,29 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>89</v>
+        <v>364</v>
       </c>
       <c r="O50" t="n">
-        <v>89</v>
+        <v>364</v>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_CN_PROV_REPORT_HIV_INFECTION</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_CN_PROV_REPORT_HIV_INFECTION</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>SRC_TW_NIDSS</t>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>人類免疫缺乏病毒感染(含母子垂直感染及孕產婦疑似個案)</t>
+          <t>HIV</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
@@ -9980,7 +9951,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -9995,7 +9966,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>country:TW:national</t>
+          <t>country:CN-GX:national</t>
         </is>
       </c>
       <c r="AD50" t="inlineStr">
@@ -10010,7 +9981,7 @@
       </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG50" t="inlineStr">
@@ -10030,17 +10001,17 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.10.16.1</t>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>NIDSS disease code 044, including source-specified vertical transmission and suspected maternal cases.</t>
+          <t>Province-reported all-stage HIV infection count. Kept separate from AIDS (D005), which is a distinct disease stage and source category.</t>
         </is>
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN50" t="b">
@@ -10063,7 +10034,7 @@
       </c>
       <c r="AS50" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_CN_PROV_REPORT_HIV_INFECTION</t>
         </is>
       </c>
       <c r="AT50" t="n">
@@ -10076,42 +10047,42 @@
       </c>
       <c r="AV50" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/fdcrbyqgb/yqyb/</t>
         </is>
       </c>
       <c r="BC50" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -10143,12 +10114,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>CA-ON</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ontario, Canada</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -10173,23 +10144,31 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N51" t="n">
-        <v>56</v>
+        <v>7</v>
       </c>
       <c r="O51" t="n">
-        <v>56</v>
+        <v>7</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0.1245166419604896</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -10199,66 +10178,75 @@
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ51" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR51" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS51" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_150</t>
+        </is>
+      </c>
       <c r="AT51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB51" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC51" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -10285,7 +10273,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -10320,37 +10308,112 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="O52" t="n">
-        <v>13</v>
-      </c>
-      <c r="R52" t="n">
-        <v>0.2312451922123379</v>
-      </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>7</v>
       </c>
       <c r="U52" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_150</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>HIV, total</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use the THL all-stage total; HIV not AIDS is an overlapping child and is not projected.</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN52" t="b">
+        <v>1</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -10449,17 +10512,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -10484,12 +10547,12 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N53" t="n">
@@ -10498,34 +10561,17 @@
       <c r="O53" t="n">
         <v>13</v>
       </c>
+      <c r="R53" t="n">
+        <v>0.2299668573534158</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
-        </is>
-      </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_150</t>
-        </is>
-      </c>
-      <c r="W53" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>HIV, total</t>
-        </is>
-      </c>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -10533,64 +10579,6 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD53" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE53" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF53" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG53" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use the THL all-stage total; HIV not AIDS is an overlapping child and is not projected.</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN53" t="b">
-        <v>1</v>
-      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -10603,7 +10591,7 @@
       </c>
       <c r="AQ53" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR53" t="inlineStr">
@@ -10613,7 +10601,7 @@
       </c>
       <c r="AS53" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AT53" t="n">
@@ -10621,47 +10609,47 @@
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC53" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -10688,7 +10676,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10723,37 +10711,112 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N54" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="O54" t="n">
-        <v>16</v>
-      </c>
-      <c r="R54" t="n">
-        <v>0.283036132127281</v>
-      </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>13</v>
       </c>
       <c r="U54" t="inlineStr">
         <is>
           <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Hiv-infeksjon</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG54" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS HIV infection kept distinct from AIDS.</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN54" t="b">
+        <v>1</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -10852,17 +10915,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -10887,48 +10950,31 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N55" t="n">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="O55" t="n">
-        <v>16</v>
+        <v>89</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0.3867666277328837</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W55" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>Hiv-infeksjon</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -10936,135 +10982,72 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD55" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE55" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF55" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG55" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI55" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS HIV infection kept distinct from AIDS.</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN55" t="b">
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP55" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ55" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS55" t="inlineStr">
+        <is>
+          <t>SER_TW_HIV_044</t>
+        </is>
+      </c>
+      <c r="AT55" t="n">
         <v>1</v>
       </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP55" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ55" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR55" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS55" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT55" t="n">
-        <v>2</v>
-      </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC55" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -11091,7 +11074,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -11126,37 +11109,112 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N56" t="n">
-        <v>37</v>
+        <v>89</v>
       </c>
       <c r="O56" t="n">
-        <v>37</v>
-      </c>
-      <c r="R56" t="n">
-        <v>0.1607906205181651</v>
-      </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>89</v>
       </c>
       <c r="U56" t="inlineStr">
         <is>
           <t>SER_TW_HIV_044</t>
         </is>
       </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>SER_TW_HIV_044</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>SRC_TW_NIDSS</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>人類免疫缺乏病毒感染(含母子垂直感染及孕產婦疑似個案)</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>country:TW:national</t>
+        </is>
+      </c>
+      <c r="AD56" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG56" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>NIDSS disease code 044, including source-specified vertical transmission and suspected maternal cases.</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN56" t="b">
+        <v>1</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -11250,17 +11308,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -11294,39 +11352,14 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="O57" t="n">
-        <v>37</v>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>SER_TW_HIV_044</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>SER_TW_HIV_044</t>
-        </is>
-      </c>
-      <c r="W57" t="inlineStr">
-        <is>
-          <t>SRC_TW_NIDSS</t>
-        </is>
-      </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>人類免疫缺乏病毒感染(含母子垂直感染及孕產婦疑似個案)</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>notification</t>
+        <v>56</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -11334,130 +11367,68 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>country:TW:national</t>
-        </is>
-      </c>
-      <c r="AD57" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE57" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF57" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG57" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI57" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.10.16.1</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>NIDSS disease code 044, including source-specified vertical transmission and suspected maternal cases.</t>
-        </is>
-      </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN57" t="b">
-        <v>1</v>
-      </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ57" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS57" t="inlineStr">
-        <is>
-          <t>SER_TW_HIV_044</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC57" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -11519,22 +11490,22 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N58" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="O58" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="R58" t="n">
-        <v>0.3201856507555447</v>
+        <v>0.2312451922123379</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -11683,19 +11654,19 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N59" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="O59" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="U59" t="inlineStr">
         <is>
@@ -11922,22 +11893,22 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N60" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O60" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R60" t="n">
-        <v>0.3184156486431911</v>
+        <v>0.283036132127281</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -12086,19 +12057,19 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N61" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O61" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
@@ -12295,12 +12266,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -12325,22 +12296,22 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N62" t="n">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="O62" t="n">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="R62" t="n">
-        <v>0.03557618341728275</v>
+        <v>0.1607906205181651</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -12349,7 +12320,7 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -12364,70 +12335,65 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ62" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR62" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="AT62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC62" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -12459,12 +12425,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -12489,38 +12455,38 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N63" t="n">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="O63" t="n">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_TW_NIDSS</t>
         </is>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>HIV, total</t>
+          <t>人類免疫缺乏病毒感染(含母子垂直感染及孕產婦疑似個案)</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
@@ -12530,7 +12496,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -12545,7 +12511,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:TW:national</t>
         </is>
       </c>
       <c r="AD63" t="inlineStr">
@@ -12560,7 +12526,7 @@
       </c>
       <c r="AF63" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG63" t="inlineStr">
@@ -12580,12 +12546,12 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Use the THL all-stage total; HIV not AIDS is an overlapping child and is not projected.</t>
+          <t>NIDSS disease code 044, including source-specified vertical transmission and suspected maternal cases.</t>
         </is>
       </c>
       <c r="AM63" t="inlineStr">
@@ -12603,70 +12569,65 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ63" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR63" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="AT63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC63" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -12698,12 +12659,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -12728,22 +12689,22 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N64" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="O64" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="R64" t="n">
-        <v>0.05306927477386519</v>
+        <v>0.3201856507555447</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -12752,7 +12713,7 @@
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -12772,7 +12733,7 @@
       </c>
       <c r="AQ64" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR64" t="inlineStr">
@@ -12782,7 +12743,7 @@
       </c>
       <c r="AS64" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AT64" t="n">
@@ -12790,47 +12751,47 @@
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC64" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -12862,12 +12823,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -12892,38 +12853,38 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N65" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="O65" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>Hiv-infeksjon</t>
+          <t>HIV, total</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr">
@@ -12948,7 +12909,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD65" t="inlineStr">
@@ -12983,17 +12944,17 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS HIV infection kept distinct from AIDS.</t>
+          <t>Finland THL national monthly notification series; Use the THL all-stage total; HIV not AIDS is an overlapping child and is not projected.</t>
         </is>
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -13011,7 +12972,7 @@
       </c>
       <c r="AQ65" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR65" t="inlineStr">
@@ -13021,7 +12982,7 @@
       </c>
       <c r="AS65" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AT65" t="n">
@@ -13029,45 +12990,1254 @@
       </c>
       <c r="AU65" t="inlineStr">
         <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV65" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA65" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB65" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC65" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>hiv-infection</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>人类免疫缺乏病毒感染</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>18</v>
+      </c>
+      <c r="O66" t="n">
+        <v>18</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0.3184156486431911</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP66" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ66" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS66" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT66" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
-      <c r="AV65" t="inlineStr">
+      <c r="AV66" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW65" t="inlineStr">
+      <c r="AW66" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
+      <c r="AX66" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY65" t="inlineStr">
+      <c r="AY66" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
+      <c r="AZ66" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA65" t="inlineStr">
+      <c r="BA66" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB65" t="inlineStr">
+      <c r="BB66" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC65" t="inlineStr">
+      <c r="BC66" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>hiv-infection</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>人类免疫缺乏病毒感染</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>18</v>
+      </c>
+      <c r="O67" t="n">
+        <v>18</v>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>Hiv-infeksjon</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD67" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG67" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS HIV infection kept distinct from AIDS.</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN67" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP67" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ67" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS67" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT67" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV67" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA67" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB67" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC67" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>hiv-infection</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>人类免疫缺乏病毒感染</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>2</v>
+      </c>
+      <c r="O68" t="n">
+        <v>2</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0.03557618341728275</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_150</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP68" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ68" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS68" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_150</t>
+        </is>
+      </c>
+      <c r="AT68" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV68" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA68" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB68" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC68" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>hiv-infection</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>人类免疫缺乏病毒感染</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>2</v>
+      </c>
+      <c r="O69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_150</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_150</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>HIV, total</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD69" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE69" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF69" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG69" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use the THL all-stage total; HIV not AIDS is an overlapping child and is not projected.</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN69" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP69" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ69" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS69" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_150</t>
+        </is>
+      </c>
+      <c r="AT69" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV69" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA69" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB69" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC69" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>hiv-infection</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>人类免疫缺乏病毒感染</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>3</v>
+      </c>
+      <c r="O70" t="n">
+        <v>3</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0.05306927477386519</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP70" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ70" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS70" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT70" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV70" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA70" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB70" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC70" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>hiv-infection</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>人类免疫缺乏病毒感染</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>3</v>
+      </c>
+      <c r="O71" t="n">
+        <v>3</v>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>Hiv-infeksjon</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF71" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG71" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS HIV infection kept distinct from AIDS.</t>
+        </is>
+      </c>
+      <c r="AM71" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN71" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP71" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ71" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR71" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS71" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT71" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV71" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA71" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB71" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC71" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -13189,7 +14359,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10">
@@ -13199,7 +14369,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11">
@@ -13219,7 +14389,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13">
@@ -13229,7 +14399,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -13251,7 +14421,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1404</v>
+        <v>2478</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d162/2026-2029.xlsx
+++ b/diseases/d162/2026-2029.xlsx
@@ -6127,13 +6127,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="O40" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="R40" t="n">
-        <v>0.05306927477386519</v>
+        <v>0.1592078243215956</v>
       </c>
       <c r="U40" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2478</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d162/2026-2029.xlsx
+++ b/diseases/d162/2026-2029.xlsx
@@ -5983,13 +5983,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O39" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R39" t="n">
-        <v>0.03557618341728275</v>
+        <v>0.07115236683456549</v>
       </c>
       <c r="U39" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2484</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d162/2026-2029.xlsx
+++ b/diseases/d162/2026-2029.xlsx
@@ -5983,13 +5983,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R39" t="n">
-        <v>0.07115236683456549</v>
+        <v>0.08894045854320688</v>
       </c>
       <c r="U39" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2486</v>
+        <v>2487</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d162/2026-2029.xlsx
+++ b/diseases/d162/2026-2029.xlsx
@@ -765,6 +765,11 @@
       <c r="O2" t="n">
         <v>71</v>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -777,13 +782,23 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV2" t="inlineStr">
         <is>
           <t>pho_idto_monthly</t>
@@ -900,6 +915,11 @@
       <c r="R3" t="n">
         <v>0.1600928253777724</v>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U3" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_150</t>
@@ -917,7 +937,17 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -926,7 +956,12 @@
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -992,17 +1027,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1036,17 +1071,39 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="O4" t="n">
-        <v>18</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.3184156486431911</v>
+        <v>9</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_150</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>HIV, total</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1054,6 +1111,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use the THL all-stage total; HIV not AIDS is an overlapping child and is not projected.</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN4" t="b">
+        <v>1</v>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -1061,55 +1176,70 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1271,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1180,17 +1310,22 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>98</v>
+        <v>18</v>
       </c>
       <c r="O5" t="n">
-        <v>98</v>
+        <v>18</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4258778597508158</v>
+        <v>0.3184156486431911</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1205,55 +1340,70 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1430,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CA-ON</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ontario, Canada</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1315,77 +1465,184 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="O6" t="n">
-        <v>59</v>
+        <v>18</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Hiv-infeksjon</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS HIV infection kept distinct from AIDS.</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN6" t="b">
+        <v>1</v>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr"/>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1674,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1447,26 +1704,26 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>13</v>
+        <v>98</v>
       </c>
       <c r="O7" t="n">
-        <v>13</v>
+        <v>98</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2312451922123379</v>
+        <v>0.4258778597508158</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1486,7 +1743,7 @@
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="AT7" t="n">
@@ -1494,42 +1751,42 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -1561,12 +1818,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1600,17 +1857,14 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>10</v>
+        <v>59</v>
       </c>
       <c r="O8" t="n">
-        <v>10</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.1768975825795506</v>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+        <v>59</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1620,60 +1874,66 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -1705,12 +1965,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1744,17 +2004,22 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>83</v>
+        <v>13</v>
       </c>
       <c r="O9" t="n">
-        <v>83</v>
+        <v>13</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3606924730542624</v>
+        <v>0.2312451922123379</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1769,55 +2034,70 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -1844,17 +2124,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CA-ON</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ontario, Canada</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1879,77 +2159,184 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="O10" t="n">
-        <v>51</v>
+        <v>13</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_150</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_150</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>HIV, total</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use the THL all-stage total; HIV not AIDS is an overlapping child and is not projected.</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN10" t="b">
+        <v>1</v>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr"/>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_150</t>
+        </is>
+      </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -1981,12 +2368,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -2011,26 +2398,31 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="O11" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3379737424641861</v>
+        <v>0.1768975825795506</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2045,55 +2437,70 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2527,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2155,33 +2562,113 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="O12" t="n">
-        <v>21</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.3714849234170563</v>
+        <v>10</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
           <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Hiv-infeksjon</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS HIV infection kept distinct from AIDS.</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN12" t="b">
+        <v>1</v>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -2189,7 +2676,17 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -2198,7 +2695,12 @@
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2299,22 +2801,22 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="O13" t="n">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="R13" t="n">
-        <v>0.460643399322311</v>
+        <v>0.3606924730542624</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
@@ -2443,19 +2945,24 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O14" t="n">
-        <v>49</v>
+        <v>51</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
@@ -2469,13 +2976,23 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
       </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV14" t="inlineStr">
         <is>
           <t>pho_idto_monthly</t>
@@ -2575,22 +3092,27 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="O15" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="R15" t="n">
-        <v>0.2134571005036965</v>
+        <v>0.3379737424641861</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -2609,7 +3131,17 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -2618,7 +3150,12 @@
         </is>
       </c>
       <c r="AT15" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2684,17 +3221,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2719,26 +3256,48 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="O16" t="n">
-        <v>11</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.1945873408375057</v>
+        <v>19</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_150</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>HIV, total</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2746,6 +3305,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use the THL all-stage total; HIV not AIDS is an overlapping child and is not projected.</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN16" t="b">
+        <v>1</v>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -2753,55 +3370,70 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AT16" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -2833,12 +3465,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2863,26 +3495,31 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>82</v>
+        <v>21</v>
       </c>
       <c r="O17" t="n">
-        <v>82</v>
+        <v>21</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3563467806078255</v>
+        <v>0.3714849234170563</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2897,55 +3534,70 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AT17" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -2972,17 +3624,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CA-ON</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ontario, Canada</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -3007,77 +3659,184 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="O18" t="n">
-        <v>53</v>
+        <v>21</v>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Hiv-infeksjon</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS HIV infection kept distinct from AIDS.</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN18" t="b">
+        <v>1</v>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS18" t="inlineStr"/>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -3109,12 +3868,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CN-GX</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Guangxi, China</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -3139,23 +3898,26 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>330</v>
+        <v>106</v>
       </c>
       <c r="O19" t="n">
-        <v>330</v>
+        <v>106</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.460643399322311</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_REPORT_HIV_INFECTION</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3175,7 +3937,7 @@
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_REPORT_HIV_INFECTION</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="AT19" t="n">
@@ -3183,42 +3945,42 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>cn_province_datacenter</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>cn_province_datacenter; cn_province_monthly_report</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/fdcrbyqgb/yqyb/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -3250,12 +4012,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3280,26 +4042,23 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="O20" t="n">
-        <v>13</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0.2312451922123379</v>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_150</t>
+        <v>49</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3309,60 +4068,66 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS20" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_150</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -3394,12 +4159,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3424,26 +4189,31 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="O21" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3891746816750113</v>
+        <v>0.2134571005036965</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3458,55 +4228,70 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AT21" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -3533,17 +4318,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3568,26 +4353,48 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>93</v>
+        <v>12</v>
       </c>
       <c r="O22" t="n">
-        <v>93</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0.4041493975186313</v>
+        <v>12</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_FI_THL_TTR_150</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_150</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>HIV, total</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3595,6 +4402,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use the THL all-stage total; HIV not AIDS is an overlapping child and is not projected.</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN22" t="b">
+        <v>1</v>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -3602,55 +4467,70 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AT22" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -3682,12 +4562,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CA-ON</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ontario, Canada</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3712,19 +4592,32 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>62</v>
+        <v>11</v>
       </c>
       <c r="O23" t="n">
-        <v>62</v>
+        <v>11</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.1945873408375057</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
@@ -3733,56 +4626,75 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS23" t="inlineStr"/>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -3809,17 +4721,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CN-GX</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Guangxi, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3844,23 +4756,48 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>380</v>
+        <v>11</v>
       </c>
       <c r="O24" t="n">
-        <v>380</v>
+        <v>11</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_REPORT_HIV_INFECTION</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Hiv-infeksjon</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3868,6 +4805,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS HIV infection kept distinct from AIDS.</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN24" t="b">
+        <v>1</v>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -3875,55 +4870,70 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_REPORT_HIV_INFECTION</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AT24" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>cn_province_datacenter</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>cn_province_datacenter; cn_province_monthly_report</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/fdcrbyqgb/yqyb/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -3955,12 +4965,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3985,26 +4995,26 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>14</v>
+        <v>82</v>
       </c>
       <c r="O25" t="n">
-        <v>14</v>
+        <v>82</v>
       </c>
       <c r="R25" t="n">
-        <v>0.2490332839209793</v>
+        <v>0.3563467806078255</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -4024,7 +5034,7 @@
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="AT25" t="n">
@@ -4032,42 +5042,42 @@
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -4099,12 +5109,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -4129,26 +5139,23 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="O26" t="n">
-        <v>16</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0.283036132127281</v>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+        <v>53</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4158,60 +5165,66 @@
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS26" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -4243,12 +5256,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>CN-GX</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Guangxi, China</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -4273,26 +5286,23 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>100</v>
+        <v>330</v>
       </c>
       <c r="O27" t="n">
-        <v>100</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0.4345692446436896</v>
+        <v>330</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_CN_PROV_REPORT_HIV_INFECTION</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4312,7 +5322,7 @@
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_CN_PROV_REPORT_HIV_INFECTION</t>
         </is>
       </c>
       <c r="AT27" t="n">
@@ -4320,42 +5330,42 @@
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/fdcrbyqgb/yqyb/</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -4387,12 +5397,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CA-ON</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ontario, Canada</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -4417,19 +5427,32 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="O28" t="n">
-        <v>47</v>
+        <v>13</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.2312451922123379</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_150</t>
+        </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
@@ -4438,56 +5461,75 @@
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS28" t="inlineStr"/>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ28" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS28" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_150</t>
+        </is>
+      </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -4514,17 +5556,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CN-GX</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Guangxi, China</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -4549,23 +5591,48 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>364</v>
+        <v>13</v>
       </c>
       <c r="O29" t="n">
-        <v>364</v>
+        <v>13</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_REPORT_HIV_INFECTION</t>
+          <t>SER_FI_THL_TTR_150</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_150</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>HIV, total</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4573,6 +5640,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use the THL all-stage total; HIV not AIDS is an overlapping child and is not projected.</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN29" t="b">
+        <v>1</v>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -4580,55 +5705,70 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ29" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_REPORT_HIV_INFECTION</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AT29" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>cn_province_datacenter</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>cn_province_datacenter; cn_province_monthly_report</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/fdcrbyqgb/yqyb/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -4660,12 +5800,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4690,26 +5830,31 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="O30" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R30" t="n">
-        <v>0.1245166419604896</v>
+        <v>0.3891746816750113</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4724,55 +5869,70 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ30" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AT30" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -4799,7 +5959,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -4834,33 +5994,113 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="O31" t="n">
-        <v>13</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0.2299668573534158</v>
+        <v>22</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
           <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Hiv-infeksjon</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS HIV infection kept distinct from AIDS.</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN31" t="b">
+        <v>1</v>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -4868,7 +6108,17 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ31" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
@@ -4877,7 +6127,12 @@
         </is>
       </c>
       <c r="AT31" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -4978,22 +6233,22 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N32" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="O32" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="R32" t="n">
-        <v>0.3867666277328837</v>
+        <v>0.4041493975186313</v>
       </c>
       <c r="U32" t="inlineStr">
         <is>
@@ -5122,19 +6377,24 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N33" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="O33" t="n">
-        <v>56</v>
+        <v>62</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
@@ -5148,13 +6408,23 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
       </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV33" t="inlineStr">
         <is>
           <t>pho_idto_monthly</t>
@@ -5224,12 +6494,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN-GX</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Guangxi, China</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -5254,26 +6524,23 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>13</v>
+        <v>380</v>
       </c>
       <c r="O34" t="n">
-        <v>13</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0.2312451922123379</v>
+        <v>380</v>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_CN_PROV_REPORT_HIV_INFECTION</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5293,7 +6560,7 @@
       </c>
       <c r="AS34" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_CN_PROV_REPORT_HIV_INFECTION</t>
         </is>
       </c>
       <c r="AT34" t="n">
@@ -5301,42 +6568,42 @@
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/fdcrbyqgb/yqyb/</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -5368,12 +6635,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -5398,26 +6665,31 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N35" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O35" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="R35" t="n">
-        <v>0.283036132127281</v>
+        <v>0.2490332839209793</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5432,55 +6704,70 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ35" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AT35" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -5507,17 +6794,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -5542,26 +6829,48 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N36" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="O36" t="n">
-        <v>37</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0.1607906205181651</v>
+        <v>14</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_FI_THL_TTR_150</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_150</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>HIV, total</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5569,6 +6878,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use the THL all-stage total; HIV not AIDS is an overlapping child and is not projected.</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN36" t="b">
+        <v>1</v>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -5576,55 +6943,70 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ36" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AT36" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -5656,12 +7038,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -5686,26 +7068,31 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N37" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O37" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R37" t="n">
-        <v>0.3201856507555447</v>
+        <v>0.283036132127281</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5720,55 +7107,70 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ37" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AT37" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC37" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -5795,7 +7197,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -5830,33 +7232,113 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N38" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O38" t="n">
-        <v>18</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0.3184156486431911</v>
+        <v>16</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
           <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Hiv-infeksjon</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS HIV infection kept distinct from AIDS.</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN38" t="b">
+        <v>1</v>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -5864,7 +7346,17 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ38" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr">
@@ -5873,7 +7365,12 @@
         </is>
       </c>
       <c r="AT38" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -5944,12 +7441,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -5974,26 +7471,26 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N39" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="O39" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="R39" t="n">
-        <v>0.08894045854320688</v>
+        <v>0.4345692446436896</v>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -6013,7 +7510,7 @@
       </c>
       <c r="AS39" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="AT39" t="n">
@@ -6021,42 +7518,42 @@
       </c>
       <c r="AV39" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC39" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -6088,117 +7585,3920 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
+          <t>CA-ON</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>人类免疫缺乏病毒感染</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>47</v>
+      </c>
+      <c r="O40" t="n">
+        <v>47</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP40" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS40" t="inlineStr"/>
+      <c r="AT40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV40" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="BA40" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="BB40" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="BC40" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>hiv-infection</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>CN-GX</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Guangxi, China</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>人类免疫缺乏病毒感染</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>364</v>
+      </c>
+      <c r="O41" t="n">
+        <v>364</v>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_HIV_INFECTION</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP41" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS41" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_HIV_INFECTION</t>
+        </is>
+      </c>
+      <c r="AT41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV41" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA41" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB41" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gxzf.gov.cn/xxgk_49493/fdzdgk/ggws/fdcrbyqgb/yqyb/</t>
+        </is>
+      </c>
+      <c r="BC41" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>hiv-infection</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>人类免疫缺乏病毒感染</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O42" t="n">
+        <v>7</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0.1245166419604896</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_150</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP42" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ42" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS42" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_150</t>
+        </is>
+      </c>
+      <c r="AT42" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV42" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA42" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB42" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC42" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>hiv-infection</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>人类免疫缺乏病毒感染</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>7</v>
+      </c>
+      <c r="O43" t="n">
+        <v>7</v>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_150</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_150</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>HIV, total</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use the THL all-stage total; HIV not AIDS is an overlapping child and is not projected.</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN43" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP43" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ43" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS43" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_150</t>
+        </is>
+      </c>
+      <c r="AT43" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV43" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA43" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB43" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC43" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>hiv-infection</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>D162</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>HIV infection</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
         <is>
           <t>人类免疫缺乏病毒感染</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>13</v>
+      </c>
+      <c r="O44" t="n">
+        <v>13</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0.2299668573534158</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP44" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ44" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS44" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT44" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV44" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA44" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB44" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC44" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>hiv-infection</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>人类免疫缺乏病毒感染</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>13</v>
+      </c>
+      <c r="O45" t="n">
+        <v>13</v>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Hiv-infeksjon</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS HIV infection kept distinct from AIDS.</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN45" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP45" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ45" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS45" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT45" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV45" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA45" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB45" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC45" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>hiv-infection</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>人类免疫缺乏病毒感染</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>89</v>
+      </c>
+      <c r="O46" t="n">
+        <v>89</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0.3867666277328837</v>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>SER_TW_HIV_044</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP46" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS46" t="inlineStr">
+        <is>
+          <t>SER_TW_HIV_044</t>
+        </is>
+      </c>
+      <c r="AT46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV46" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA46" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB46" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC46" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>hiv-infection</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>CA-ON</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>人类免疫缺乏病毒感染</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>56</v>
+      </c>
+      <c r="O47" t="n">
+        <v>56</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP47" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS47" t="inlineStr"/>
+      <c r="AT47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV47" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="BA47" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="BB47" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="BC47" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>hiv-infection</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>人类免疫缺乏病毒感染</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>13</v>
+      </c>
+      <c r="O48" t="n">
+        <v>13</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0.2312451922123379</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_150</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP48" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ48" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS48" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_150</t>
+        </is>
+      </c>
+      <c r="AT48" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV48" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA48" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB48" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC48" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>hiv-infection</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>人类免疫缺乏病毒感染</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>13</v>
+      </c>
+      <c r="O49" t="n">
+        <v>13</v>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_150</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_150</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>HIV, total</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG49" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use the THL all-stage total; HIV not AIDS is an overlapping child and is not projected.</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN49" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP49" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ49" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS49" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_150</t>
+        </is>
+      </c>
+      <c r="AT49" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV49" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA49" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB49" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC49" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>hiv-infection</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>人类免疫缺乏病毒感染</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>16</v>
+      </c>
+      <c r="O50" t="n">
+        <v>16</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0.283036132127281</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP50" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ50" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT50" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV50" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA50" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB50" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC50" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>hiv-infection</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>人类免疫缺乏病毒感染</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>16</v>
+      </c>
+      <c r="O51" t="n">
+        <v>16</v>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Hiv-infeksjon</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG51" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS HIV infection kept distinct from AIDS.</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN51" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP51" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ51" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT51" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV51" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA51" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB51" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC51" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>hiv-infection</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>人类免疫缺乏病毒感染</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>37</v>
+      </c>
+      <c r="O52" t="n">
+        <v>37</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0.1607906205181651</v>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>SER_TW_HIV_044</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP52" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr">
+        <is>
+          <t>SER_TW_HIV_044</t>
+        </is>
+      </c>
+      <c r="AT52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV52" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA52" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB52" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC52" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>hiv-infection</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>人类免疫缺乏病毒感染</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>18</v>
+      </c>
+      <c r="O53" t="n">
+        <v>18</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0.3201856507555447</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_150</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP53" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ53" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_150</t>
+        </is>
+      </c>
+      <c r="AT53" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV53" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA53" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB53" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC53" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>hiv-infection</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>人类免疫缺乏病毒感染</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>18</v>
+      </c>
+      <c r="O54" t="n">
+        <v>18</v>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_150</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_150</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>HIV, total</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG54" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use the THL all-stage total; HIV not AIDS is an overlapping child and is not projected.</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN54" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP54" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ54" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS54" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_150</t>
+        </is>
+      </c>
+      <c r="AT54" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV54" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA54" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB54" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC54" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>hiv-infection</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>人类免疫缺乏病毒感染</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>18</v>
+      </c>
+      <c r="O55" t="n">
+        <v>18</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0.3184156486431911</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP55" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ55" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS55" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT55" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV55" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA55" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB55" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC55" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>hiv-infection</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>人类免疫缺乏病毒感染</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>18</v>
+      </c>
+      <c r="O56" t="n">
+        <v>18</v>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Hiv-infeksjon</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD56" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG56" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS HIV infection kept distinct from AIDS.</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN56" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP56" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ56" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT56" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV56" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA56" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB56" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC56" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>hiv-infection</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>人类免疫缺乏病毒感染</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="N40" t="n">
+      <c r="N57" t="n">
+        <v>7</v>
+      </c>
+      <c r="O57" t="n">
+        <v>7</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0.1245166419604896</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_150</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP57" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ57" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_150</t>
+        </is>
+      </c>
+      <c r="AT57" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV57" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA57" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB57" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC57" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>hiv-infection</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>人类免疫缺乏病毒感染</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>7</v>
+      </c>
+      <c r="O58" t="n">
+        <v>7</v>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_150</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_150</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>HIV, total</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD58" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG58" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use the THL all-stage total; HIV not AIDS is an overlapping child and is not projected.</t>
+        </is>
+      </c>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN58" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP58" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ58" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS58" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_150</t>
+        </is>
+      </c>
+      <c r="AT58" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV58" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA58" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB58" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC58" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>hiv-infection</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>人类免疫缺乏病毒感染</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
         <v>9</v>
       </c>
-      <c r="O40" t="n">
+      <c r="O59" t="n">
         <v>9</v>
       </c>
-      <c r="R40" t="n">
+      <c r="R59" t="n">
         <v>0.1592078243215956</v>
       </c>
-      <c r="U40" t="inlineStr">
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
         <is>
           <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
-      <c r="AA40" t="inlineStr">
+      <c r="AA59" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AO40" t="inlineStr">
+      <c r="AO59" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP40" t="inlineStr">
-        <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS40" t="inlineStr">
+      <c r="AP59" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ59" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR59" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS59" t="inlineStr">
         <is>
           <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
-      <c r="AT40" t="n">
+      <c r="AT59" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV59" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA59" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB59" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC59" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>hiv-infection</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>人类免疫缺乏病毒感染</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>9</v>
+      </c>
+      <c r="O60" t="n">
+        <v>9</v>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>Hiv-infeksjon</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD60" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG60" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS HIV infection kept distinct from AIDS.</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN60" t="b">
         <v>1</v>
       </c>
-      <c r="AV40" t="inlineStr">
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP60" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ60" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS60" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT60" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV60" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW40" t="inlineStr">
+      <c r="AW60" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
+      <c r="AX60" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY40" t="inlineStr">
+      <c r="AY60" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
+      <c r="AZ60" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA40" t="inlineStr">
+      <c r="BA60" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB40" t="inlineStr">
+      <c r="BB60" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC40" t="inlineStr">
+      <c r="BC60" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -6330,7 +11630,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11">
@@ -6350,7 +11650,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -6360,7 +11660,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -6382,7 +11682,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2487</v>
+        <v>2489</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d162/2026-2029.xlsx
+++ b/diseases/d162/2026-2029.xlsx
@@ -9009,13 +9009,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O48" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R48" t="n">
-        <v>0.2312451922123379</v>
+        <v>0.2490332839209793</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -9173,10 +9173,10 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O49" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
@@ -9959,13 +9959,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O53" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R53" t="n">
-        <v>0.3201856507555447</v>
+        <v>0.3023975590469034</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -10123,10 +10123,10 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O54" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="U54" t="inlineStr">
         <is>
